--- a/data/specialthanks-dun.xlsx
+++ b/data/specialthanks-dun.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiayuankevinguo/Desktop/life-final/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3621491-CC30-6F4C-AAAD-675F0E6B9680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09541EA-D165-F04D-8EA6-8AFF9205067C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="&gt;specialthanks&lt;arr&gt;" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>group</t>
   </si>
@@ -82,6 +82,12 @@
   </si>
   <si>
     <t>俺想圈很多很多钱，有很多很多粉丝，然后写很多很多小说，做很多很多游戏。</t>
+  </si>
+  <si>
+    <t>MKStoler</t>
+  </si>
+  <si>
+    <t>一般不想贬低任何游戏</t>
   </si>
 </sst>
 </file>
@@ -542,9 +548,17 @@
       <c r="A10" s="1">
         <v>1</v>
       </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="2"/>
+      <c r="A11" s="1">
+        <v>1</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
